--- a/results/表6_水分浓度.xlsx
+++ b/results/表6_水分浓度.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.75" defaultRowHeight="14.1" customHeight="1"/>
   <cols>
     <col width="19.625" customWidth="1" style="2" min="1" max="1"/>
@@ -640,7 +640,7 @@
     <row r="1" ht="14.1" customHeight="1" s="4">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>时间\到药材中心的距离</t>
+          <t>时间/h\到药材中心的距离/cm</t>
         </is>
       </c>
       <c r="B1" s="1" t="n">
@@ -666,154 +666,193 @@
     </row>
     <row r="2" ht="14.1" customHeight="1" s="4">
       <c r="A2" s="1" t="n">
-        <v>21600</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>1.7188</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1.53702</v>
+        <v>1.537</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>1.02215</v>
+        <v>1.0221</v>
       </c>
       <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
+      <c r="F2" s="5" t="n">
+        <v>0.4205</v>
+      </c>
       <c r="G2" s="5" t="n">
-        <v>0.4205234903273569</v>
+        <v>0.4205</v>
       </c>
     </row>
     <row r="3" ht="14.1" customHeight="1" s="4">
       <c r="A3" s="1" t="n">
-        <v>43200</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.73736</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.65435</v>
+        <v>0.6544</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.40816</v>
+        <v>0.4082</v>
       </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="5" t="n">
+        <v>0.1669</v>
+      </c>
       <c r="G3" s="5" t="n">
-        <v>0.1668857705137443</v>
+        <v>0.1669</v>
       </c>
     </row>
     <row r="4" ht="14.1" customHeight="1" s="4">
       <c r="A4" s="1" t="n">
-        <v>64800</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.40864</v>
+        <v>0.4086</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.36855</v>
+        <v>0.3686</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.23969</v>
+        <v>0.2397</v>
       </c>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>0.0892</v>
+      </c>
       <c r="G4" s="5" t="n">
-        <v>0.0891630534122803</v>
+        <v>0.0892</v>
       </c>
     </row>
     <row r="5" ht="14.1" customHeight="1" s="4">
       <c r="A5" s="1" t="n">
-        <v>86400</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.28507</v>
+        <v>0.2851</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.26102</v>
+        <v>0.261</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.17899</v>
+        <v>0.179</v>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="5" t="n">
+        <v>0.0673</v>
+      </c>
       <c r="G5" s="5" t="n">
-        <v>0.06732409158757878</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>108000</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.22631</v>
+        <v>0.2263</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.20938</v>
+        <v>0.2094</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.14929</v>
+        <v>0.1493</v>
       </c>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="5" t="n">
+        <v>0.0595</v>
+      </c>
       <c r="G6" s="5" t="n">
-        <v>0.05948597315437686</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>129600</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.19282</v>
+        <v>0.1928</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.17966</v>
+        <v>0.1797</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.13169</v>
+        <v>0.1317</v>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>0.056</v>
+      </c>
       <c r="G7" s="5" t="n">
-        <v>0.05596313854394679</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>151200</v>
+        <v>42</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.17124</v>
+        <v>0.1712</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.16038</v>
+        <v>0.1604</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.12001</v>
+        <v>0.12</v>
       </c>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>0.0541</v>
+      </c>
       <c r="G8" s="5" t="n">
-        <v>0.05410636959894522</v>
+        <v>0.0541</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>172800</v>
+        <v>48</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.15616</v>
+        <v>0.1562</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.14682</v>
+        <v>0.1468</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.11159</v>
+        <v>0.1116</v>
       </c>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="5" t="n">
+        <v>0.053</v>
+      </c>
       <c r="G9" s="5" t="n">
-        <v>0.05301478027741752</v>
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>烘干结束时间=51.0974 h</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.0526</v>
       </c>
     </row>
   </sheetData>
